--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_9248711583CF9423E851EEDB953E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{755844A7-6771-4ED9-8593-024815D32592}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="11_9248711583CF9423E851EEDB953E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDB5DA4-E265-484E-8EB5-D9FDE24E95C9}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="48">
   <si>
     <t>ResponseId</t>
   </si>
@@ -177,13 +177,20 @@
   </si>
   <si>
     <t>2026-03-22T19:45:42.8842352Z</t>
+  </si>
+  <si>
+    <t>anargyros.megalios@uzh.ch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan-Akim Albert Reimer
+</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +202,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,10 +230,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -239,8 +256,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE71E5D-2FC8-4A7C-9471-2FA3E1955E04}" name="Responses" displayName="Responses" ref="A1:N11" totalsRowShown="0">
-  <autoFilter ref="A1:N11" xr:uid="{6FE71E5D-2FC8-4A7C-9471-2FA3E1955E04}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6FE71E5D-2FC8-4A7C-9471-2FA3E1955E04}" name="Responses" displayName="Responses" ref="A1:N14" totalsRowShown="0">
+  <autoFilter ref="A1:N14" xr:uid="{6FE71E5D-2FC8-4A7C-9471-2FA3E1955E04}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{FB89DE1D-4C11-4761-8D11-788CCF566045}" name="ResponseId"/>
     <tableColumn id="2" xr3:uid="{EAB2BAF6-0686-4B33-A477-A5DC980B3E48}" name="SubmittedAt"/>
@@ -558,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1030,6 +1047,129 @@
         <v>45</v>
       </c>
     </row>
+    <row r="12" spans="1:14" ht="15.75">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="48.75">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="48.75">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/PeerGrading/Input/form_exports/forms_responses.xlsx
+++ b/PeerGrading/Input/form_exports/forms_responses.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_9248711583CF9423E851EEDB953E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EDB5DA4-E265-484E-8EB5-D9FDE24E95C9}"/>
+  <xr:revisionPtr revIDLastSave="136" documentId="11_9248711583CF9423E851EEDB953E8C1851038385" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD62D8FE-2D31-4446-8DBD-4A035E36E887}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -234,8 +234,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1020,13 +1020,13 @@
         <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
